--- a/Employee_Reports_wi48/Sameera Lakmal Rupasinghe Arachchige Q0577.xlsx
+++ b/Employee_Reports_wi48/Sameera Lakmal Rupasinghe Arachchige Q0577.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-60</v>
+        <v>-63</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-59</v>
+        <v>-62</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-55</v>
+        <v>-58</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-46</v>
+        <v>-49</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-48</v>
+        <v>-51</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-52</v>
+        <v>-55</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-33</v>
+        <v>-36</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-54</v>
+        <v>-57</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-76</v>
+        <v>-79</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-402</v>
+        <v>-405</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-425</v>
+        <v>-428</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1461,11 +1461,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-340</v>
+        <v>-343</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-340</v>
+        <v>-343</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-125</v>
+        <v>-128</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1596,11 +1596,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-122</v>
+        <v>-125</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1619,9 +1619,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr"/>
-      <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr"/>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
           <t>25-Mar-2025</t>
@@ -1633,11 +1645,11 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-110</v>
+        <v>-113</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1670,11 +1682,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
